--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142887</v>
+        <v>121142891</v>
       </c>
       <c r="B2" t="n">
-        <v>97237</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489280</v>
+        <v>489274</v>
       </c>
       <c r="R2" t="n">
-        <v>6540836</v>
+        <v>6540821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>121142888</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142890</v>
+        <v>121142889</v>
       </c>
       <c r="B4" t="n">
         <v>8421</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489362</v>
+        <v>489338</v>
       </c>
       <c r="R4" t="n">
-        <v>6540877</v>
+        <v>6540837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142889</v>
+        <v>121142890</v>
       </c>
       <c r="B5" t="n">
         <v>8421</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489338</v>
+        <v>489362</v>
       </c>
       <c r="R5" t="n">
-        <v>6540837</v>
+        <v>6540877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142891</v>
+        <v>121142887</v>
       </c>
       <c r="B6" t="n">
-        <v>100337</v>
+        <v>97247</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489274</v>
+        <v>489280</v>
       </c>
       <c r="R6" t="n">
-        <v>6540821</v>
+        <v>6540836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142891</v>
+        <v>121142890</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489274</v>
+        <v>489362</v>
       </c>
       <c r="R2" t="n">
-        <v>6540821</v>
+        <v>6540877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +762,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142890</v>
+        <v>121142887</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>97247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,32 +1035,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>220250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489362</v>
+        <v>489280</v>
       </c>
       <c r="R5" t="n">
-        <v>6540877</v>
+        <v>6540836</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,18 +1105,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142887</v>
+        <v>121142891</v>
       </c>
       <c r="B6" t="n">
-        <v>97247</v>
+        <v>100347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489280</v>
+        <v>489274</v>
       </c>
       <c r="R6" t="n">
-        <v>6540836</v>
+        <v>6540821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142888</v>
+        <v>121142891</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489277</v>
+        <v>489274</v>
       </c>
       <c r="R3" t="n">
-        <v>6540820</v>
+        <v>6540821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142889</v>
+        <v>121142888</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,32 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489338</v>
+        <v>489277</v>
       </c>
       <c r="R4" t="n">
-        <v>6540837</v>
+        <v>6540820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,18 +988,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142887</v>
+        <v>121142889</v>
       </c>
       <c r="B5" t="n">
-        <v>97247</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1028,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489280</v>
+        <v>489338</v>
       </c>
       <c r="R5" t="n">
-        <v>6540836</v>
+        <v>6540837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,12 +1099,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142891</v>
+        <v>121142887</v>
       </c>
       <c r="B6" t="n">
-        <v>100347</v>
+        <v>97260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489274</v>
+        <v>489280</v>
       </c>
       <c r="R6" t="n">
-        <v>6540821</v>
+        <v>6540836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142890</v>
+        <v>121142889</v>
       </c>
       <c r="B2" t="n">
         <v>8421</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489362</v>
+        <v>489338</v>
       </c>
       <c r="R2" t="n">
-        <v>6540877</v>
+        <v>6540837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -795,7 +795,7 @@
         <v>121142891</v>
       </c>
       <c r="B3" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142888</v>
+        <v>121142890</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,31 +918,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489277</v>
+        <v>489362</v>
       </c>
       <c r="R4" t="n">
-        <v>6540820</v>
+        <v>6540877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,12 +989,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142889</v>
+        <v>121142888</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,32 +1035,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489338</v>
+        <v>489277</v>
       </c>
       <c r="R5" t="n">
-        <v>6540837</v>
+        <v>6540820</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,18 +1105,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>121142887</v>
       </c>
       <c r="B6" t="n">
-        <v>97260</v>
+        <v>97261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142889</v>
+        <v>121142888</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489338</v>
+        <v>489277</v>
       </c>
       <c r="R2" t="n">
-        <v>6540837</v>
+        <v>6540820</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,18 +761,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142891</v>
+        <v>121142890</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +801,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489274</v>
+        <v>489362</v>
       </c>
       <c r="R3" t="n">
-        <v>6540821</v>
+        <v>6540877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +872,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142890</v>
+        <v>121142889</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489362</v>
+        <v>489338</v>
       </c>
       <c r="R4" t="n">
-        <v>6540877</v>
+        <v>6540837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142888</v>
+        <v>121142891</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489277</v>
+        <v>489274</v>
       </c>
       <c r="R5" t="n">
-        <v>6540820</v>
+        <v>6540821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>121142887</v>
       </c>
       <c r="B6" t="n">
-        <v>97261</v>
+        <v>97264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 38918-2022 artfynd.xlsx
+++ b/artfynd/A 38918-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121142888</v>
+        <v>121142889</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>8424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489277</v>
+        <v>489338</v>
       </c>
       <c r="R2" t="n">
-        <v>6540820</v>
+        <v>6540837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +762,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142890</v>
+        <v>121142891</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489362</v>
+        <v>489274</v>
       </c>
       <c r="R3" t="n">
-        <v>6540877</v>
+        <v>6540821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,18 +878,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142889</v>
+        <v>121142890</v>
       </c>
       <c r="B4" t="n">
         <v>8424</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489338</v>
+        <v>489362</v>
       </c>
       <c r="R4" t="n">
-        <v>6540837</v>
+        <v>6540877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142891</v>
+        <v>121142887</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
+        <v>97264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489274</v>
+        <v>489280</v>
       </c>
       <c r="R5" t="n">
-        <v>6540821</v>
+        <v>6540836</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121142887</v>
+        <v>121142888</v>
       </c>
       <c r="B6" t="n">
-        <v>97264</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489280</v>
+        <v>489277</v>
       </c>
       <c r="R6" t="n">
-        <v>6540836</v>
+        <v>6540820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
